--- a/data/processed/other_sites_processed.xlsx
+++ b/data/processed/other_sites_processed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,15 +439,10 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Landform_agri_score</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>Soil_agri_score</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Aquifer_productivity</t>
         </is>
@@ -455,1197 +450,1041 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>268.43102</v>
+        <v>1412.124522</v>
       </c>
       <c r="D2" t="n">
-        <v>67.590149</v>
+        <v>949.337528</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1111.007758</v>
+        <v>3121.066619</v>
       </c>
       <c r="D3" t="n">
-        <v>222.717869</v>
+        <v>72.17397800000001</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>218.569687</v>
+        <v>2788.607699</v>
       </c>
       <c r="D4" t="n">
-        <v>229.341642</v>
+        <v>651.9859760000001</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1330.284718</v>
+        <v>577.7614610000001</v>
       </c>
       <c r="D5" t="n">
-        <v>598.345965</v>
+        <v>494.650966</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>762.967528</v>
+        <v>5287.614871</v>
       </c>
       <c r="D6" t="n">
-        <v>98.56748899999999</v>
+        <v>357.069301</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>385.141475</v>
+        <v>2308.969669</v>
       </c>
       <c r="D7" t="n">
-        <v>166.673373</v>
+        <v>992.909022</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>32.903106</v>
+        <v>3012.266277</v>
       </c>
       <c r="D8" t="n">
-        <v>440.067211</v>
+        <v>826.791689</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1412.124522</v>
+        <v>4334.008889</v>
       </c>
       <c r="D9" t="n">
-        <v>949.337528</v>
+        <v>339.956896</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>3121.066619</v>
+        <v>2782.3243</v>
       </c>
       <c r="D10" t="n">
-        <v>72.17397800000001</v>
+        <v>240.315498</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2788.607699</v>
+        <v>2932.058855</v>
       </c>
       <c r="D11" t="n">
-        <v>651.9859760000001</v>
+        <v>976.5688</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>577.7614610000001</v>
+        <v>3655.704469</v>
       </c>
       <c r="D12" t="n">
-        <v>494.650966</v>
+        <v>43.145679</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>5287.614871</v>
+        <v>1681.063582</v>
       </c>
       <c r="D13" t="n">
-        <v>357.069301</v>
+        <v>1776.250521</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2308.969669</v>
+        <v>3517.133622</v>
       </c>
       <c r="D14" t="n">
-        <v>992.909022</v>
+        <v>1123.121372</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>4128.906285</v>
+        <v>4690.979741</v>
       </c>
       <c r="D15" t="n">
-        <v>353.81195</v>
+        <v>277.881844</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>2226.822283</v>
+        <v>2426.398267</v>
       </c>
       <c r="D16" t="n">
-        <v>1497.11381</v>
+        <v>1891.701064</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1447.528635</v>
+        <v>2221.124323</v>
       </c>
       <c r="D17" t="n">
-        <v>57.350916</v>
+        <v>496.84417</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
-      </c>
-      <c r="G17" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1858.577247</v>
+        <v>799.030827</v>
       </c>
       <c r="D18" t="n">
-        <v>614.845384</v>
+        <v>1119.470833</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>987.080562</v>
+        <v>149.578152</v>
       </c>
       <c r="D19" t="n">
-        <v>29.69766</v>
+        <v>1427.042157</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1273.77869</v>
+        <v>604.891288</v>
       </c>
       <c r="D20" t="n">
-        <v>2.011753</v>
+        <v>581.175914</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
-      </c>
-      <c r="G20" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B21" t="n">
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>3012.266277</v>
+        <v>848.027316</v>
       </c>
       <c r="D21" t="n">
-        <v>826.791689</v>
+        <v>1223.72538</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>4334.008889</v>
+        <v>5137.960913</v>
       </c>
       <c r="D22" t="n">
-        <v>339.956896</v>
+        <v>339.32631</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>2782.3243</v>
+        <v>1116.296126</v>
       </c>
       <c r="D23" t="n">
-        <v>240.315498</v>
+        <v>1734.065377</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B24" t="n">
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2932.058855</v>
+        <v>1058.368042</v>
       </c>
       <c r="D24" t="n">
-        <v>976.5688</v>
+        <v>1170.095051</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>3655.704469</v>
+        <v>5014.419378</v>
       </c>
       <c r="D25" t="n">
-        <v>43.145679</v>
+        <v>838.955992</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1681.063582</v>
+        <v>256.06471</v>
       </c>
       <c r="D26" t="n">
-        <v>1776.250521</v>
+        <v>1993.699024</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>3517.133622</v>
+        <v>304.947149</v>
       </c>
       <c r="D27" t="n">
-        <v>1123.121372</v>
+        <v>1034.728325</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>4690.979741</v>
+        <v>173.853318</v>
       </c>
       <c r="D28" t="n">
-        <v>277.881844</v>
+        <v>1880.982124</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
       </c>
       <c r="F28" t="n">
         <v>4</v>
-      </c>
-      <c r="G28" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>2071.372352</v>
+        <v>268.43102</v>
       </c>
       <c r="D29" t="n">
-        <v>156.603329</v>
+        <v>67.590149</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1627.701551</v>
+        <v>1111.007758</v>
       </c>
       <c r="D30" t="n">
-        <v>522.427405</v>
+        <v>222.717869</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>155.181518</v>
+        <v>218.569687</v>
       </c>
       <c r="D31" t="n">
-        <v>191.365314</v>
+        <v>229.341642</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>641.811589</v>
+        <v>1330.284718</v>
       </c>
       <c r="D32" t="n">
-        <v>692.3326530000001</v>
+        <v>598.345965</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>882.235578</v>
+        <v>762.967528</v>
       </c>
       <c r="D33" t="n">
-        <v>140.005488</v>
+        <v>98.56748899999999</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>2426.398267</v>
+        <v>385.141475</v>
       </c>
       <c r="D34" t="n">
-        <v>1891.701064</v>
+        <v>166.673373</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>2221.124323</v>
+        <v>32.903106</v>
       </c>
       <c r="D35" t="n">
-        <v>496.84417</v>
+        <v>440.067211</v>
       </c>
       <c r="E35" t="n">
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>799.030827</v>
+        <v>4128.906285</v>
       </c>
       <c r="D36" t="n">
-        <v>1119.470833</v>
+        <v>353.81195</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
         <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>149.578152</v>
+        <v>2226.822283</v>
       </c>
       <c r="D37" t="n">
-        <v>1427.042157</v>
+        <v>1497.11381</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>604.891288</v>
+        <v>1447.528635</v>
       </c>
       <c r="D38" t="n">
-        <v>581.175914</v>
+        <v>57.350916</v>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>4892.34282</v>
+        <v>1858.577247</v>
       </c>
       <c r="D39" t="n">
-        <v>814.461462</v>
+        <v>614.845384</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>4905.25557</v>
+        <v>987.080562</v>
       </c>
       <c r="D40" t="n">
-        <v>800.313575</v>
+        <v>29.69766</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>5006.335316</v>
+        <v>1273.77869</v>
       </c>
       <c r="D41" t="n">
-        <v>47.121753</v>
+        <v>2.011753</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>4738.276906</v>
+        <v>2071.372352</v>
       </c>
       <c r="D42" t="n">
-        <v>263.249472</v>
+        <v>156.603329</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>114.765688</v>
+        <v>1627.701551</v>
       </c>
       <c r="D43" t="n">
-        <v>2894.9376</v>
+        <v>522.427405</v>
       </c>
       <c r="E43" t="n">
         <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>3961.357005</v>
+        <v>155.181518</v>
       </c>
       <c r="D44" t="n">
-        <v>666.556386</v>
+        <v>191.365314</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>148.106099</v>
+        <v>641.811589</v>
       </c>
       <c r="D45" t="n">
-        <v>2579.307208</v>
+        <v>692.3326530000001</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
-      </c>
-      <c r="G45" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>848.027316</v>
+        <v>882.235578</v>
       </c>
       <c r="D46" t="n">
-        <v>1223.72538</v>
+        <v>140.005488</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>5137.960913</v>
+        <v>4892.34282</v>
       </c>
       <c r="D47" t="n">
-        <v>339.32631</v>
+        <v>814.461462</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>1116.296126</v>
+        <v>4905.25557</v>
       </c>
       <c r="D48" t="n">
-        <v>1734.065377</v>
+        <v>800.313575</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>1058.368042</v>
+        <v>5006.335316</v>
       </c>
       <c r="D49" t="n">
-        <v>1170.095051</v>
+        <v>47.121753</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>5014.419378</v>
+        <v>4738.276906</v>
       </c>
       <c r="D50" t="n">
-        <v>838.955992</v>
+        <v>263.249472</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>256.06471</v>
+        <v>114.765688</v>
       </c>
       <c r="D51" t="n">
-        <v>1993.699024</v>
+        <v>2894.9376</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>304.947149</v>
+        <v>3961.357005</v>
       </c>
       <c r="D52" t="n">
-        <v>1034.728325</v>
+        <v>666.556386</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>173.853318</v>
+        <v>148.106099</v>
       </c>
       <c r="D53" t="n">
-        <v>1880.982124</v>
+        <v>2579.307208</v>
       </c>
       <c r="E53" t="n">
         <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
-      </c>
-      <c r="G53" t="n">
         <v>4</v>
       </c>
     </row>
